--- a/artfynd/A 20244-2026 artfynd.xlsx
+++ b/artfynd/A 20244-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84217431</v>
+        <v>84217440</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>99017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219795</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84217440</v>
+        <v>84217439</v>
       </c>
       <c r="B3" t="n">
-        <v>98558</v>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219795</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84217439</v>
+        <v>84217431</v>
       </c>
       <c r="B4" t="n">
-        <v>98693</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 20244-2026 artfynd.xlsx
+++ b/artfynd/A 20244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84217440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84217439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84217431</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>